--- a/ig/DM_FINESS_New/ValueSet-vs-tre-r278-engagement-all.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-vs-tre-r278-engagement-all.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_R278-FinessConvention/FHIR/TRE-R278-FinessConvention?vs</t>
+    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r278-engagement?vs</t>
   </si>
   <si>
     <t>Identifier</t>
@@ -105,7 +105,7 @@
     <t>System URI</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_R278-FinessConvention/FHIR/TRE-R278-FinessConvention</t>
+    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r278-engagement</t>
   </si>
 </sst>
 </file>
